--- a/语文群_20260826.xlsx
+++ b/语文群_20260826.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huil\checkin\WeChatTextExport\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huil\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1041,7 +1041,7 @@
     <row r="1" spans="1:4">
       <c r="B1">
         <f>SUM(B3:B10000)</f>
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1244,10 +1244,10 @@
       </c>
       <c r="B15" s="2">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="2">
         <v>25</v>
